--- a/metrics_all.xlsx
+++ b/metrics_all.xlsx
@@ -487,31 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6635024305587806</v>
+        <v>0.6431751961629666</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6631965464934342</v>
+        <v>0.642280224432376</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6638083146241269</v>
+        <v>0.6440701678935572</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9025436714679742</v>
+        <v>0.6038803366415992</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.5997822931785196</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.6043228418440643</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.1406569094622192</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9025436714679742</v>
+        <v>0.9332620709128313</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.227874276261373</v>
       </c>
     </row>
     <row r="3">
@@ -521,31 +521,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6651469585017874</v>
+        <v>0.670859672784875</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6647257525011649</v>
+        <v>0.6703363915077374</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6655681645024099</v>
+        <v>0.6713829540620126</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9027558405431528</v>
+        <v>0.9033805605978453</v>
       </c>
       <c r="F3" t="n">
-        <v>0.009192065795839382</v>
+        <v>0.02588292210933721</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9992425231814026</v>
+        <v>0.9981324278438031</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5671641791044776</v>
+        <v>0.5994397759103641</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9032867397053268</v>
+        <v>0.9046649542500681</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01809093073077839</v>
+        <v>0.0496231884057971</v>
       </c>
     </row>
     <row r="4">
@@ -555,31 +555,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6267122349445591</v>
+        <v>0.6381761483321656</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6262192081328462</v>
+        <v>0.6375839021180084</v>
       </c>
       <c r="D4" t="n">
-        <v>0.627205261756272</v>
+        <v>0.6387683945463228</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9030151583017044</v>
+        <v>0.901836441217379</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006531204644412192</v>
+        <v>0.02116594097726173</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9998171607679248</v>
+        <v>0.9969309128901659</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7941176470588235</v>
+        <v>0.4268292682926829</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9031025126813731</v>
+        <v>0.9041431752499171</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01295585412667946</v>
+        <v>0.04033187370361835</v>
       </c>
     </row>
     <row r="5">
@@ -589,31 +589,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6564452898552784</v>
+        <v>0.5984472186455327</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6560556797811419</v>
+        <v>0.5955175347170647</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6568348999294149</v>
+        <v>0.6013769025740008</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9021193333176171</v>
+        <v>0.5876965510738112</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004233188195452347</v>
+        <v>0.5619254958877601</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9990727438944756</v>
+        <v>0.59047929998694</v>
       </c>
       <c r="H5" t="n">
-        <v>0.330188679245283</v>
+        <v>0.1290448018220704</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9028348203748289</v>
+        <v>0.9258318828708918</v>
       </c>
       <c r="J5" t="n">
-        <v>0.008359207069500836</v>
+        <v>0.2098890921822412</v>
       </c>
     </row>
     <row r="6">
@@ -623,31 +623,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6764097537887583</v>
+        <v>0.628220603323974</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6760169136574249</v>
+        <v>0.6270656897737044</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6768025939200918</v>
+        <v>0.6293755168742436</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9031448171809803</v>
+        <v>0.8601923666281619</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01245766811804548</v>
+        <v>0.1591678761490082</v>
       </c>
       <c r="G6" t="n">
-        <v>0.999320882852292</v>
+        <v>0.9358887292673371</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6645161290322581</v>
+        <v>0.2114056224899598</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9035815925274258</v>
+        <v>0.9115667892078918</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02445684435474297</v>
+        <v>0.1816049127164838</v>
       </c>
     </row>
     <row r="7">
@@ -657,31 +657,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6434274135893815</v>
+        <v>0.529105114488079</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6431063818377323</v>
+        <v>0.5268795375809912</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6437484453410307</v>
+        <v>0.5313306913951668</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9024140125886985</v>
+        <v>0.8121360711002146</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0004837929366231253</v>
+        <v>0.177552007740687</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9998041008227766</v>
+        <v>0.8806582212354708</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.1384122194983971</v>
       </c>
       <c r="I7" t="n">
-        <v>0.902568999870312</v>
+        <v>0.9083953012178037</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0009653674429829854</v>
+        <v>0.1555579103528664</v>
       </c>
     </row>
     <row r="8">
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6695786197956798</v>
+        <v>0.6291124374084596</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6690445774761545</v>
+        <v>0.6289058097031659</v>
       </c>
       <c r="D8" t="n">
-        <v>0.670112662115205</v>
+        <v>0.6293190651137532</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9033923477686886</v>
+        <v>0.8381503571512765</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02999516207063377</v>
+        <v>0.2131107885824867</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9977014496539115</v>
+        <v>0.9056418963040356</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5849056603773585</v>
+        <v>0.1960609769667297</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9049920629279503</v>
+        <v>0.9142265757867398</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05706396686608375</v>
+        <v>0.2042306577803535</v>
       </c>
     </row>
     <row r="9">
@@ -725,31 +725,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6119559951561314</v>
+        <v>0.6514884230567993</v>
       </c>
       <c r="C9" t="n">
-        <v>0.609452276403068</v>
+        <v>0.6504925080682892</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6144597139091948</v>
+        <v>0.6524843380453095</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7065112331738136</v>
+        <v>0.6107168957306868</v>
       </c>
       <c r="F9" t="n">
-        <v>0.410982099661345</v>
+        <v>0.6071601354620223</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7384223586260937</v>
+        <v>0.6111009533759958</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1450463140820421</v>
+        <v>0.1442611644347376</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9206982462425298</v>
+        <v>0.9350919264588329</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2144186780249251</v>
+        <v>0.2331305438164678</v>
       </c>
     </row>
     <row r="10">
@@ -759,31 +759,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5259263320528016</v>
+        <v>0.6449786343214727</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5237676094432772</v>
+        <v>0.6444132239575892</v>
       </c>
       <c r="D10" t="n">
-        <v>0.528085054662326</v>
+        <v>0.6455440446853563</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8178882104717226</v>
+        <v>0.9010820622834107</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1632801161103048</v>
+        <v>0.01584421867440735</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8885725479952984</v>
+        <v>0.9966697139872013</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1366120218579235</v>
+        <v>0.3393782383419689</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9077058541010726</v>
+        <v>0.9036494103159191</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1487603305785124</v>
+        <v>0.03027501733302519</v>
       </c>
     </row>
     <row r="11">
@@ -793,31 +793,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6811183900139375</v>
+        <v>0.6755508538910582</v>
       </c>
       <c r="C11" t="n">
-        <v>0.680664626712434</v>
+        <v>0.6750759250849033</v>
       </c>
       <c r="D11" t="n">
-        <v>0.681572153315441</v>
+        <v>0.676025782697213</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9035337938188076</v>
+        <v>0.90318017869351</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02237542331881955</v>
+        <v>0.02564102564102564</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9986809455400287</v>
+        <v>0.9979365286665796</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6468531468531469</v>
+        <v>0.572972972972973</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9044020247894786</v>
+        <v>0.9046266041577876</v>
       </c>
       <c r="J11" t="n">
-        <v>0.04325461772270283</v>
+        <v>0.04908543644362121</v>
       </c>
     </row>
     <row r="12">
@@ -827,31 +827,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6153743721118762</v>
+        <v>0.6450908607315062</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6132806324517185</v>
+        <v>0.6443026416875146</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6174681117720339</v>
+        <v>0.6458790797754979</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6896150715199442</v>
+        <v>0.5999036432807802</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4291720816451342</v>
+        <v>0.6080574879596361</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7213643353059037</v>
+        <v>0.5989096500629048</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1580829555374088</v>
+        <v>0.1559821936344204</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9120214909335125</v>
+        <v>0.926116467078812</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2310573321809277</v>
+        <v>0.2482754315322908</v>
       </c>
     </row>
     <row r="13">
@@ -861,31 +861,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5281014915253086</v>
+        <v>0.632049762124707</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5262150466030242</v>
+        <v>0.6318858231194947</v>
       </c>
       <c r="D13" t="n">
-        <v>0.529987936447593</v>
+        <v>0.6322137011299193</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8021447676640141</v>
+        <v>0.845139800309006</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1779680452564789</v>
+        <v>0.1494534057029279</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8782349377941382</v>
+        <v>0.9299473463491915</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1512277510718462</v>
+        <v>0.2063978040540541</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8975826729655593</v>
+        <v>0.899688046594659</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1635118525021949</v>
+        <v>0.1733693965326121</v>
       </c>
     </row>
     <row r="14">
@@ -895,31 +895,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6797121330318441</v>
+        <v>0.67469910956611</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6793721214915561</v>
+        <v>0.674213550883639</v>
       </c>
       <c r="D14" t="n">
-        <v>0.680052144572132</v>
+        <v>0.675184668248581</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8917315966972904</v>
+        <v>0.8908012559599954</v>
       </c>
       <c r="F14" t="n">
-        <v>0.005427719593303264</v>
+        <v>0.01972326274749637</v>
       </c>
       <c r="G14" t="n">
-        <v>0.999776338474442</v>
+        <v>0.9969898886351988</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7473684210526316</v>
+        <v>0.4440619621342513</v>
       </c>
       <c r="I14" t="n">
-        <v>0.891845607734577</v>
+        <v>0.8929677392429365</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01077717061323619</v>
+        <v>0.03776899429073342</v>
       </c>
     </row>
     <row r="15">
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6726351668729427</v>
+        <v>0.6341536038186772</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6723009114107236</v>
+        <v>0.6329698672032522</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6729694223351618</v>
+        <v>0.6353373404341023</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8913411858521755</v>
+        <v>0.7323110660708055</v>
       </c>
       <c r="F15" t="n">
-        <v>7.644675483525724e-05</v>
+        <v>0.4064673954590627</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9999906807697684</v>
+        <v>0.7720329900750198</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5</v>
+        <v>0.1785486416602304</v>
       </c>
       <c r="I15" t="n">
-        <v>0.891347687400319</v>
+        <v>0.9143112563047006</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0001528701368187724</v>
+        <v>0.2481101259916006</v>
       </c>
     </row>
     <row r="16">
@@ -963,31 +963,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.660283395290731</v>
+        <v>0.5294680614231811</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6599460686864093</v>
+        <v>0.5274677762487497</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6606207218950527</v>
+        <v>0.5314683465976126</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8910587609854966</v>
+        <v>0.7877078730084893</v>
       </c>
       <c r="F16" t="n">
-        <v>0.002522742909563489</v>
+        <v>0.1995260301200214</v>
       </c>
       <c r="G16" t="n">
-        <v>0.999375611574484</v>
+        <v>0.8594100927263408</v>
       </c>
       <c r="H16" t="n">
-        <v>0.33</v>
+        <v>0.1474909584086799</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8915251982774388</v>
+        <v>0.8980329145973318</v>
       </c>
       <c r="J16" t="n">
-        <v>0.005007207343904104</v>
+        <v>0.1696071741885174</v>
       </c>
     </row>
     <row r="17">
@@ -997,31 +997,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6476579756016625</v>
+        <v>0.6510250428362396</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6473666754559458</v>
+        <v>0.6504817112301833</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6479492757473791</v>
+        <v>0.651568374442296</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8913494924659013</v>
+        <v>0.8861495522735202</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0006115740386820579</v>
+        <v>0.02033483678617843</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9999347653883789</v>
+        <v>0.9916965658636596</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.22990492653414</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8913941065539042</v>
+        <v>0.8925177599409539</v>
       </c>
       <c r="J17" t="n">
-        <v>0.001221747098350641</v>
+        <v>0.03736479842674533</v>
       </c>
     </row>
     <row r="18">
@@ -1031,31 +1031,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.683708865979449</v>
+        <v>0.6763613358011209</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6833159103126983</v>
+        <v>0.6759153115983881</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6841018216461997</v>
+        <v>0.6768073600038537</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8923130596580998</v>
+        <v>0.8910670675992225</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01475422368320465</v>
+        <v>0.01528935096705145</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9992917385023997</v>
+        <v>0.9978286193560412</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7174721189591078</v>
+        <v>0.4618937644341801</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8927046130023227</v>
+        <v>0.8926162747075939</v>
       </c>
       <c r="J18" t="n">
-        <v>0.02891385767790262</v>
+        <v>0.02959893443836022</v>
       </c>
     </row>
     <row r="19">
@@ -1065,31 +1065,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6679034194475636</v>
+        <v>0.6553227792261356</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6676318694565881</v>
+        <v>0.6544605906909661</v>
       </c>
       <c r="D19" t="n">
-        <v>0.668174969438539</v>
+        <v>0.6561849677613051</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8913411858521755</v>
+        <v>0.609015998538036</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.6196773946945953</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0.6077163226317506</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.1614741035856574</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8913411858521755</v>
+        <v>0.9291169179038554</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.2561906417408069</v>
       </c>
     </row>
     <row r="20">
@@ -1099,31 +1099,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.633703670798908</v>
+        <v>0.5979511706888473</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6332674522993124</v>
+        <v>0.5954632776361034</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6341398892985036</v>
+        <v>0.6004390637415912</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8915654644227734</v>
+        <v>0.5683717375774592</v>
       </c>
       <c r="F20" t="n">
-        <v>0.003134316948245547</v>
+        <v>0.5826771653543307</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9998695307767579</v>
+        <v>0.5666278365407017</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7454545454545455</v>
+        <v>0.1408221709006929</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8916322477167147</v>
+        <v>0.9176136792381643</v>
       </c>
       <c r="J20" t="n">
-        <v>0.006242387332521315</v>
+        <v>0.2268249858643573</v>
       </c>
     </row>
     <row r="21">
@@ -1133,31 +1133,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6754532587082964</v>
+        <v>0.6479055265154737</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6749948307476302</v>
+        <v>0.6473114117356842</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6759116866689626</v>
+        <v>0.6484996412952633</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8916817570149352</v>
+        <v>0.8862658448656821</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01957036923782585</v>
+        <v>0.02943200061157404</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9979963655002096</v>
+        <v>0.9907180466893435</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5435244161358811</v>
+        <v>0.278783490224475</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8930492432139432</v>
+        <v>0.8933154069156758</v>
       </c>
       <c r="J21" t="n">
-        <v>0.03778040141676505</v>
+        <v>0.05324298160696999</v>
       </c>
     </row>
     <row r="22">
@@ -1167,31 +1167,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6458708655546941</v>
+        <v>0.6556073801535397</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6455735553414992</v>
+        <v>0.654745282275136</v>
       </c>
       <c r="D22" t="n">
-        <v>0.646168175767889</v>
+        <v>0.6564694780319434</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8912415064874654</v>
+        <v>0.6095393152027644</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0008409143031878297</v>
+        <v>0.6201360752236068</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9997856577046736</v>
+        <v>0.6082475187549509</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3235294117647059</v>
+        <v>0.1617579612753993</v>
       </c>
       <c r="I22" t="n">
-        <v>0.891401887795799</v>
+        <v>0.9292538120933411</v>
       </c>
       <c r="J22" t="n">
-        <v>0.001677468547464735</v>
+        <v>0.2565870631029575</v>
       </c>
     </row>
     <row r="23">
@@ -1201,31 +1201,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.529635742024258</v>
+        <v>0.6812596545819941</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5277564326037539</v>
+        <v>0.6808621454680006</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5315150514447621</v>
+        <v>0.6816571636959876</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8036233449072151</v>
+        <v>0.8920887810875019</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1795734271080193</v>
+        <v>0.01429554315419311</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8796980569404967</v>
+        <v>0.9990960346675365</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1539520251671254</v>
+        <v>0.6584507042253521</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8979149227608249</v>
+        <v>0.8926412549333067</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1657786089840855</v>
+        <v>0.02798353909465021</v>
       </c>
     </row>
     <row r="24">
@@ -1235,31 +1235,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6605729867546211</v>
+        <v>0.598314230971454</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6602339946391751</v>
+        <v>0.5958298233660703</v>
       </c>
       <c r="D24" t="n">
-        <v>0.660911978870067</v>
+        <v>0.6007986385768377</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8910836808266742</v>
+        <v>0.5697007957735949</v>
       </c>
       <c r="F24" t="n">
-        <v>0.003210763703080804</v>
+        <v>0.5815304640318019</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9993196961930945</v>
+        <v>0.5682587018312287</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3652173913043478</v>
+        <v>0.141040140910355</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8915865004864015</v>
+        <v>0.917623512061519</v>
       </c>
       <c r="J24" t="n">
-        <v>0.006365565322825098</v>
+        <v>0.227020413035693</v>
       </c>
     </row>
     <row r="25">
@@ -1269,31 +1269,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6793533594099135</v>
+        <v>0.6223645756032633</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6788983723990857</v>
+        <v>0.6222094651535695</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6798083464207413</v>
+        <v>0.6225196860529572</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8921552339973087</v>
+        <v>0.8398817138205439</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0205641770506842</v>
+        <v>0.1525877226511735</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9984064116303993</v>
+        <v>0.9236661851731047</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6113636363636363</v>
+        <v>0.1959359968587415</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8931852667033499</v>
+        <v>0.8994092505376636</v>
       </c>
       <c r="J25" t="n">
-        <v>0.03978995636417425</v>
+        <v>0.1715660993639333</v>
       </c>
     </row>
     <row r="26">
@@ -1303,31 +1303,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6780496773960125</v>
+        <v>0.6785138314855982</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6777196430824743</v>
+        <v>0.6780690309058721</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6783797117095507</v>
+        <v>0.6789586320653243</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8913744123070789</v>
+        <v>0.8920721678600502</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0006115740386820579</v>
+        <v>0.01689473281859185</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9999627230790736</v>
+        <v>0.9987605423791994</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6242937853107344</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8913968132653231</v>
+        <v>0.892861903492402</v>
       </c>
       <c r="J26" t="n">
-        <v>0.001222027037348201</v>
+        <v>0.03289914402679568</v>
       </c>
     </row>
     <row r="27">
@@ -1337,31 +1337,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6814161907202231</v>
+        <v>0.5256503141913178</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6810703750795372</v>
+        <v>0.523713999791001</v>
       </c>
       <c r="D27" t="n">
-        <v>0.681762006360909</v>
+        <v>0.5275866285916346</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8917399033110163</v>
+        <v>0.7948432541989933</v>
       </c>
       <c r="F27" t="n">
-        <v>0.00527482608363275</v>
+        <v>0.1817139362434065</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9998042961651368</v>
+        <v>0.8695866921392293</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.1451957730132551</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8918334774223582</v>
+        <v>0.8970917656107292</v>
       </c>
       <c r="J27" t="n">
-        <v>0.01047756434591147</v>
+        <v>0.1614151840282494</v>
       </c>
     </row>
     <row r="28">
@@ -1371,31 +1371,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6344742530902525</v>
+        <v>0.6443281795886124</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6340404825571506</v>
+        <v>0.643820521410629</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6349080236233544</v>
+        <v>0.6448358377665959</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8915405445815958</v>
+        <v>0.8904191517286063</v>
       </c>
       <c r="F28" t="n">
-        <v>0.002752083174069261</v>
+        <v>0.01276660805748796</v>
       </c>
       <c r="G28" t="n">
-        <v>0.999888169237221</v>
+        <v>0.99740925399562</v>
       </c>
       <c r="H28" t="n">
-        <v>0.75</v>
+        <v>0.3752808988764045</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8915970017783243</v>
+        <v>0.8923303957779242</v>
       </c>
       <c r="J28" t="n">
-        <v>0.005484042958336507</v>
+        <v>0.02469318349844743</v>
       </c>
     </row>
     <row r="29">
@@ -1405,31 +1405,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.671159492662417</v>
+        <v>0.6460746368892243</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6708895197037875</v>
+        <v>0.6452877052065076</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6714294656210466</v>
+        <v>0.646861568571941</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8913411858521755</v>
+        <v>0.5978685229179472</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.6118033789465637</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0.5961697963748195</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.1558944989870656</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8913411858521755</v>
+        <v>0.9264590876176684</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.2484747815017775</v>
       </c>
     </row>
     <row r="30">
@@ -1439,31 +1439,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.616081794372934</v>
+        <v>0.6315501638272728</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6139771777165451</v>
+        <v>0.6305238713267234</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6181864110293228</v>
+        <v>0.6325764563278222</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6851128868805343</v>
+        <v>0.836858106424335</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4398746273220702</v>
+        <v>0.1778915985016436</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7150086202879642</v>
+        <v>0.9171893201621546</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1583597082702628</v>
+        <v>0.207526977615268</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9128267361482909</v>
+        <v>0.901495791083876</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2328800388538125</v>
+        <v>0.1915699349633654</v>
       </c>
     </row>
     <row r="31">
@@ -1473,31 +1473,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6866610358264202</v>
+        <v>0.6535634722736567</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6862669413290713</v>
+        <v>0.6530737050738726</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6870551303237692</v>
+        <v>0.6540532394734409</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8923213662718257</v>
+        <v>0.8893475985579719</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01429554315419311</v>
+        <v>0.01154345998012384</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9993569731140208</v>
+        <v>0.9963561809794511</v>
       </c>
       <c r="H31" t="n">
-        <v>0.73046875</v>
+        <v>0.2785977859778598</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8926662781986182</v>
+        <v>0.8921097426654651</v>
       </c>
       <c r="J31" t="n">
-        <v>0.02804228837069806</v>
+        <v>0.02216839169052338</v>
       </c>
     </row>
     <row r="32">
@@ -1507,31 +1507,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6794067057870821</v>
+        <v>0.6510851918026495</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6790738951767286</v>
+        <v>0.6506008689119045</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6797395163974356</v>
+        <v>0.6515695146933944</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8917066768561128</v>
+        <v>0.8891233199873739</v>
       </c>
       <c r="F32" t="n">
-        <v>0.004663252044950692</v>
+        <v>0.0105496521672655</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9998415730860631</v>
+        <v>0.9962257117562089</v>
       </c>
       <c r="H32" t="n">
-        <v>0.782051282051282</v>
+        <v>0.2541436464088398</v>
       </c>
       <c r="I32" t="n">
-        <v>0.891777770389334</v>
+        <v>0.8920003671470174</v>
       </c>
       <c r="J32" t="n">
-        <v>0.009271221217417736</v>
+        <v>0.02025836758661186</v>
       </c>
     </row>
     <row r="33">
@@ -1541,31 +1541,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.684803496877821</v>
+        <v>0.6460656175898793</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6844078186616088</v>
+        <v>0.6452767779240748</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6851991750940333</v>
+        <v>0.6468544572556839</v>
       </c>
       <c r="E33" t="n">
-        <v>0.892354592726729</v>
+        <v>0.6011413287259316</v>
       </c>
       <c r="F33" t="n">
-        <v>0.01628315877990979</v>
+        <v>0.6065285528629309</v>
       </c>
       <c r="G33" t="n">
-        <v>0.999151950048926</v>
+        <v>0.6004845999720423</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7006578947368421</v>
+        <v>0.1561688056058578</v>
       </c>
       <c r="I33" t="n">
-        <v>0.892839892739961</v>
+        <v>0.9260297203299704</v>
       </c>
       <c r="J33" t="n">
-        <v>0.03182667164736645</v>
+        <v>0.2483838146669797</v>
       </c>
     </row>
     <row r="34">
@@ -1575,31 +1575,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6674031959972719</v>
+        <v>0.632516212715986</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6670575902374308</v>
+        <v>0.6313444098862484</v>
       </c>
       <c r="D34" t="n">
-        <v>0.667748801757113</v>
+        <v>0.6336880155457236</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8913411858521755</v>
+        <v>0.711120894456166</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>0.4336824401804144</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0.7449419877918084</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>0.1716905756310151</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8913411858521755</v>
+        <v>0.9151859314892837</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.2459944062615181</v>
       </c>
     </row>
     <row r="35">
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5250267304497364</v>
+        <v>0.6549492676701174</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5231481583354739</v>
+        <v>0.6540891539011642</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5269053025639988</v>
+        <v>0.6558093814390706</v>
       </c>
       <c r="E35" t="n">
-        <v>0.801928795707142</v>
+        <v>0.6087003472164537</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1712407308309762</v>
+        <v>0.6201360752236068</v>
       </c>
       <c r="G35" t="n">
-        <v>0.8788127300684964</v>
+        <v>0.607306276501561</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1469430595644188</v>
+        <v>0.1614328358208955</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8968918224876833</v>
+        <v>0.9291519333865632</v>
       </c>
       <c r="J35" t="n">
-        <v>0.1581641659311562</v>
+        <v>0.2561778591842858</v>
       </c>
     </row>
     <row r="36">
@@ -1643,31 +1643,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6597958209446946</v>
+        <v>0.598236696343783</v>
       </c>
       <c r="C36" t="n">
-        <v>0.6594605672848389</v>
+        <v>0.5957510965217134</v>
       </c>
       <c r="D36" t="n">
-        <v>0.6601310746045502</v>
+        <v>0.6007222961658525</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8910587609854966</v>
+        <v>0.5694848238167228</v>
       </c>
       <c r="F36" t="n">
-        <v>0.002064062380551946</v>
+        <v>0.5814540172769666</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9994315269558735</v>
+        <v>0.5680257210754391</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3068181818181818</v>
+        <v>0.1409588761837691</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8914861427455153</v>
+        <v>0.9175786954099989</v>
       </c>
       <c r="J36" t="n">
-        <v>0.004100539144961652</v>
+        <v>0.226909307875895</v>
       </c>
     </row>
     <row r="37">
@@ -1677,31 +1677,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6160686412280558</v>
+        <v>0.5221765011267481</v>
       </c>
       <c r="C37" t="n">
-        <v>0.6139614779905576</v>
+        <v>0.5202493967257047</v>
       </c>
       <c r="D37" t="n">
-        <v>0.6181758044655541</v>
+        <v>0.5241036055277914</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6844981974648215</v>
+        <v>0.794693735151928</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4411742221542695</v>
+        <v>0.1739928140050455</v>
       </c>
       <c r="G37" t="n">
-        <v>0.7141605703368902</v>
+        <v>0.8703601882484506</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1583568860960953</v>
+        <v>0.1406066596651634</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9129170985073204</v>
+        <v>0.8963041871802992</v>
       </c>
       <c r="J37" t="n">
-        <v>0.2330587190049269</v>
+        <v>0.1555282219488862</v>
       </c>
     </row>
     <row r="38">
@@ -1711,31 +1711,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6330711133531757</v>
+        <v>0.6272421877541632</v>
       </c>
       <c r="C38" t="n">
-        <v>0.6326390019974576</v>
+        <v>0.6270876891833129</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6335032247088938</v>
+        <v>0.6273966863250134</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8915322379678701</v>
+        <v>0.8461615137972854</v>
       </c>
       <c r="F38" t="n">
-        <v>0.002446296154728232</v>
+        <v>0.1499885329867747</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9999161269279158</v>
+        <v>0.9310283770560551</v>
       </c>
       <c r="H38" t="n">
-        <v>0.7804878048780488</v>
+        <v>0.2095482217238065</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8915700693838547</v>
+        <v>0.899849580717509</v>
       </c>
       <c r="J38" t="n">
-        <v>0.004877305288827923</v>
+        <v>0.174835145250401</v>
       </c>
     </row>
     <row r="39">
@@ -1745,31 +1745,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6457743668883767</v>
+        <v>0.6803281198304111</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6454781814511031</v>
+        <v>0.679930333070315</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6460705523256504</v>
+        <v>0.6807259065905071</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8913245726247238</v>
+        <v>0.891864502516904</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0005351272838468007</v>
+        <v>0.01536579772188671</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9999161269279158</v>
+        <v>0.9987139462280415</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4375</v>
+        <v>0.5929203539823009</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8913848965689125</v>
+        <v>0.8927086890967705</v>
       </c>
       <c r="J39" t="n">
-        <v>0.001068947087119188</v>
+        <v>0.02995529061102832</v>
       </c>
     </row>
     <row r="40">
@@ -1779,31 +1779,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.678725097173956</v>
+        <v>0.675382486774072</v>
       </c>
       <c r="C40" t="n">
-        <v>0.6782675479897352</v>
+        <v>0.6749363457401127</v>
       </c>
       <c r="D40" t="n">
-        <v>0.6791826463581768</v>
+        <v>0.6758286278080312</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8919891017227917</v>
+        <v>0.892188460452212</v>
       </c>
       <c r="F40" t="n">
-        <v>0.02262823943123615</v>
+        <v>0.018423667915297</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9979684078095149</v>
+        <v>0.9987046269978099</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5758754863813229</v>
+        <v>0.6342105263157894</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8933445675387079</v>
+        <v>0.8930053497325133</v>
       </c>
       <c r="J40" t="n">
-        <v>0.04354542111070246</v>
+        <v>0.03580714657157715</v>
       </c>
     </row>
     <row r="41">
@@ -1813,31 +1813,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6685685546595241</v>
+        <v>0.6454377283083617</v>
       </c>
       <c r="C41" t="n">
-        <v>0.6683064960022249</v>
+        <v>0.6449358933927382</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6688306133168234</v>
+        <v>0.6459395632239852</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8913411858521755</v>
+        <v>0.8904606847972356</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>0.01483067043803991</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0.9972042309305251</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>0.3927125506072874</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8913411858521755</v>
+        <v>0.8925115937677243</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>0.02858195211786372</v>
       </c>
     </row>
   </sheetData>
